--- a/6501.T_report.xlsx
+++ b/6501.T_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,58 +449,1201 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>手数料込み利益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>手数料(円)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>決済後資産(円)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>保有日数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>決済理由</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>バックテスト結果</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="I2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2022-05-30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2022-06-15</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1278.66</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1256.34</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1983</v>
+      </c>
+      <c r="I2" t="n">
+        <v>980563</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>総取引回数</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="M2" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
-      <c r="I3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1318.26</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1265.56</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-4.19</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1922</v>
+      </c>
+      <c r="I3" t="n">
+        <v>939442</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>勝率</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>59.3%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="I4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2022-12-05</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1399.88</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1344.74</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1842</v>
+      </c>
+      <c r="I4" t="n">
+        <v>900597</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>総利益率</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>76.70%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="I5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1382.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1471.68</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1859</v>
+      </c>
+      <c r="I5" t="n">
+        <v>956558</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>平均保有日数</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.0日</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>12.4日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023-04-21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1489.28</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1439.57</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-3.53</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1881</v>
+      </c>
+      <c r="I6" t="n">
+        <v>922747</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>最終資産</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1767023</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1505.46</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1596.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1901</v>
+      </c>
+      <c r="I7" t="n">
+        <v>976647</v>
+      </c>
+      <c r="J7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>手数料込み利益</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>767023</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2023-05-24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1558.27</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1657.09</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2015</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1036567</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>総手数料</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>74389</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2023-07-31</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1670.04</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1788.25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2147</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1107794</v>
+      </c>
+      <c r="J9" t="n">
+        <v>52</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1847.91</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1748.44</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2156</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1046007</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1837.31</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1950.19</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2156</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1108114</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2023-12-07</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2031.34</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1960.39</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-3.49</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2178</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1067229</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2024-01-11</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1990.54</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2141.69</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2215</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1146052</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2268.38</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2415.09</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2366</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1217810</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2024-03-21</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2658.91</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2840.62</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2519</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1298515</v>
+      </c>
+      <c r="J15" t="n">
+        <v>21</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3048.84</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3235.12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2676</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1375175</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3310.09</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3568.11</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2858</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1479510</v>
+      </c>
+      <c r="J17" t="n">
+        <v>14</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024-06-28</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3523.39</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3743.87</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="G18" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3052</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1569042</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3772.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4070.98</v>
+      </c>
+      <c r="F19" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3262</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1689745</v>
+      </c>
+      <c r="J19" t="n">
+        <v>36</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4234.88</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4096.07</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3324</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1631035</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4363.51</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4638.2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3365</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1730346</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4827.06</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5282.27</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3624</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1889901</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4974.35</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5313.06</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3908</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2014676</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>5058.95</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4737.95</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-6.35</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-6.54</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3902</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1882937</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5044.02</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5408.41</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3902</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2015062</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5238.1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5053.81</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-3.71</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3959</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1940208</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>5304.78</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5072.68</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3796</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1851522</v>
+      </c>
+      <c r="J27" t="n">
+        <v>13</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5790.48</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5537.54</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-4.56</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3622</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1767023</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
         </is>
       </c>
     </row>

--- a/6501.T_report.xlsx
+++ b/6501.T_report.xlsx
@@ -508,7 +508,7 @@
         <v>1983</v>
       </c>
       <c r="I2" t="n">
-        <v>980563</v>
+        <v>980564</v>
       </c>
       <c r="J2" t="n">
         <v>16</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1767023</v>
+        <v>1767022</v>
       </c>
     </row>
     <row r="7">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>767023</v>
+        <v>767022</v>
       </c>
     </row>
     <row r="8">
@@ -980,7 +980,7 @@
         <v>2178</v>
       </c>
       <c r="I12" t="n">
-        <v>1067229</v>
+        <v>1067230</v>
       </c>
       <c r="J12" t="n">
         <v>6</v>
@@ -1062,7 +1062,7 @@
         <v>2366</v>
       </c>
       <c r="I14" t="n">
-        <v>1217810</v>
+        <v>1217809</v>
       </c>
       <c r="J14" t="n">
         <v>21</v>
@@ -1226,7 +1226,7 @@
         <v>3052</v>
       </c>
       <c r="I18" t="n">
-        <v>1569042</v>
+        <v>1569041</v>
       </c>
       <c r="J18" t="n">
         <v>11</v>
@@ -1267,7 +1267,7 @@
         <v>3262</v>
       </c>
       <c r="I19" t="n">
-        <v>1689745</v>
+        <v>1689744</v>
       </c>
       <c r="J19" t="n">
         <v>36</v>
@@ -1390,7 +1390,7 @@
         <v>3624</v>
       </c>
       <c r="I22" t="n">
-        <v>1889901</v>
+        <v>1889900</v>
       </c>
       <c r="J22" t="n">
         <v>2</v>
@@ -1431,7 +1431,7 @@
         <v>3908</v>
       </c>
       <c r="I23" t="n">
-        <v>2014676</v>
+        <v>2014675</v>
       </c>
       <c r="J23" t="n">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3902</v>
       </c>
       <c r="I25" t="n">
-        <v>2015062</v>
+        <v>2015061</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -1554,7 +1554,7 @@
         <v>3959</v>
       </c>
       <c r="I26" t="n">
-        <v>1940208</v>
+        <v>1940207</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -1595,7 +1595,7 @@
         <v>3796</v>
       </c>
       <c r="I27" t="n">
-        <v>1851522</v>
+        <v>1851521</v>
       </c>
       <c r="J27" t="n">
         <v>13</v>
@@ -1636,7 +1636,7 @@
         <v>3622</v>
       </c>
       <c r="I28" t="n">
-        <v>1767023</v>
+        <v>1767022</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
